--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdintovaluationduration/TrdIntoValuationDuration001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdintovaluationduration/TrdIntoValuationDuration001.xlsx
@@ -62,10 +62,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交易日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>计息开始日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -74,7 +70,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交割日</t>
+    <t>交易日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交割日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -497,13 +497,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>14</v>
